--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967C7CD8-9937-4512-8DD0-06AFC0CB4991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC58B8D-F708-43AC-B59B-7659F78C8BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12960" yWindow="3830" windowWidth="13950" windowHeight="11890" activeTab="1" xr2:uid="{EA2824C1-1697-4288-88B1-60A32E5E15B0}"/>
+    <workbookView xWindow="10210" yWindow="1990" windowWidth="22360" windowHeight="16580" activeTab="1" xr2:uid="{EA2824C1-1697-4288-88B1-60A32E5E15B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="3" r:id="rId1"/>
@@ -1511,16 +1511,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>35793</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>13897</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>4260</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>35793</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>13897</xdr:colOff>
       <xdr:row>162</xdr:row>
-      <xdr:rowOff>83088</xdr:rowOff>
+      <xdr:rowOff>78828</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1535,8 +1535,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21252050" y="4260"/>
-          <a:ext cx="0" cy="25994085"/>
+          <a:off x="21932345" y="0"/>
+          <a:ext cx="0" cy="25680276"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -5142,40 +5142,40 @@
         <v>215911</v>
       </c>
       <c r="BR24" s="8">
-        <f>+BQ24*1.9</f>
-        <v>410230.89999999997</v>
+        <f>SUM(AE24:AH24)</f>
+        <v>367615</v>
       </c>
       <c r="BS24" s="8">
         <f>+BR24*1.7</f>
-        <v>697392.52999999991</v>
+        <v>624945.5</v>
       </c>
       <c r="BT24" s="8">
         <f>+BS24*1.4</f>
-        <v>976349.54199999978</v>
+        <v>874923.7</v>
       </c>
       <c r="BU24" s="8">
         <f>+BT24*1.3</f>
-        <v>1269254.4045999998</v>
+        <v>1137400.81</v>
       </c>
       <c r="BV24" s="8">
         <f>+BU24*1.3</f>
-        <v>1650030.7259799999</v>
+        <v>1478621.0530000001</v>
       </c>
       <c r="BW24" s="8">
         <f t="shared" ref="BW24:BZ24" si="8">+BV24*1.3</f>
-        <v>2145039.9437739998</v>
+        <v>1922207.3689000001</v>
       </c>
       <c r="BX24" s="8">
         <f t="shared" si="8"/>
-        <v>2788551.9269061997</v>
+        <v>2498869.5795700001</v>
       </c>
       <c r="BY24" s="8">
         <f t="shared" si="8"/>
-        <v>3625117.5049780598</v>
+        <v>3248530.4534410001</v>
       </c>
       <c r="BZ24" s="8">
         <f t="shared" si="8"/>
-        <v>4712652.7564714774</v>
+        <v>4223089.5894733006</v>
       </c>
     </row>
     <row r="25" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5358,23 +5358,23 @@
       </c>
       <c r="BR25" s="2">
         <f>+BR24-BR26</f>
-        <v>102557.72499999998</v>
+        <v>91903.75</v>
       </c>
       <c r="BS25" s="2">
         <f t="shared" ref="BS25:BT25" si="9">+BS24-BS26</f>
-        <v>153426.35659999994</v>
+        <v>137488.01</v>
       </c>
       <c r="BT25" s="2">
         <f t="shared" si="9"/>
-        <v>214796.89923999994</v>
+        <v>192483.21399999992</v>
       </c>
       <c r="BU25" s="2">
         <f t="shared" ref="BU25" si="10">+BU24-BU26</f>
-        <v>279235.9690119999</v>
+        <v>250228.17819999997</v>
       </c>
       <c r="BV25" s="2">
         <f t="shared" ref="BV25" si="11">+BV24-BV26</f>
-        <v>363006.75971559994</v>
+        <v>325296.63165999996</v>
       </c>
     </row>
     <row r="26" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5611,23 +5611,23 @@
       </c>
       <c r="BR26" s="2">
         <f>+BR24*0.75</f>
-        <v>307673.17499999999</v>
+        <v>275711.25</v>
       </c>
       <c r="BS26" s="2">
         <f>+BS24*0.78</f>
-        <v>543966.17339999997</v>
+        <v>487457.49</v>
       </c>
       <c r="BT26" s="2">
         <f>+BT24*0.78</f>
-        <v>761552.64275999984</v>
+        <v>682440.48600000003</v>
       </c>
       <c r="BU26" s="2">
         <f t="shared" ref="BU26:BV26" si="18">+BU24*0.78</f>
-        <v>990018.43558799988</v>
+        <v>887172.63180000009</v>
       </c>
       <c r="BV26" s="2">
         <f t="shared" si="18"/>
-        <v>1287023.9662643999</v>
+        <v>1153324.4213400001</v>
       </c>
     </row>
     <row r="27" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6525,23 +6525,23 @@
       </c>
       <c r="BR30" s="2">
         <f>+BR26-BR29</f>
-        <v>279981.97499999998</v>
+        <v>248020.05</v>
       </c>
       <c r="BS30" s="2">
         <f t="shared" si="58"/>
-        <v>510736.73339999997</v>
+        <v>454228.05</v>
       </c>
       <c r="BT30" s="2">
         <f t="shared" si="58"/>
-        <v>721677.31475999986</v>
+        <v>642565.15800000005</v>
       </c>
       <c r="BU30" s="2">
         <f t="shared" ref="BU30" si="59">+BU26-BU29</f>
-        <v>942168.04198799992</v>
+        <v>839322.23820000014</v>
       </c>
       <c r="BV30" s="2">
         <f t="shared" ref="BV30" si="60">+BV26-BV29</f>
-        <v>1229603.4939444</v>
+        <v>1095903.9490200002</v>
       </c>
     </row>
     <row r="31" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7012,23 +7012,23 @@
       </c>
       <c r="BR32" s="2">
         <f>+BR30+BR31</f>
-        <v>284486.47499999998</v>
+        <v>252524.55</v>
       </c>
       <c r="BS32" s="2">
         <f t="shared" si="71"/>
-        <v>515691.68339999998</v>
+        <v>459183</v>
       </c>
       <c r="BT32" s="2">
         <f t="shared" si="71"/>
-        <v>727127.75975999981</v>
+        <v>648015.603</v>
       </c>
       <c r="BU32" s="2">
         <f t="shared" ref="BU32" si="72">+BU30+BU31</f>
-        <v>948163.53148799995</v>
+        <v>845317.72770000016</v>
       </c>
       <c r="BV32" s="2">
         <f t="shared" ref="BV32" si="73">+BV30+BV31</f>
-        <v>1236198.5323944001</v>
+        <v>1102498.9874700003</v>
       </c>
     </row>
     <row r="33" spans="2:170" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7216,23 +7216,23 @@
       </c>
       <c r="BR33" s="2">
         <f>+BR32*0.2</f>
-        <v>56897.294999999998</v>
+        <v>50504.91</v>
       </c>
       <c r="BS33" s="2">
         <f t="shared" ref="BS33:BT33" si="75">+BS32*0.2</f>
-        <v>103138.33668000001</v>
+        <v>91836.6</v>
       </c>
       <c r="BT33" s="2">
         <f t="shared" si="75"/>
-        <v>145425.55195199998</v>
+        <v>129603.12060000001</v>
       </c>
       <c r="BU33" s="2">
         <f t="shared" ref="BU33" si="76">+BU32*0.2</f>
-        <v>189632.7062976</v>
+        <v>169063.54554000005</v>
       </c>
       <c r="BV33" s="2">
         <f t="shared" ref="BV33" si="77">+BV32*0.2</f>
-        <v>247239.70647888002</v>
+        <v>220499.79749400006</v>
       </c>
     </row>
     <row r="34" spans="2:170" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7469,407 +7469,407 @@
       </c>
       <c r="BR34" s="2">
         <f>+BR32-BR33</f>
-        <v>227589.18</v>
+        <v>202019.63999999998</v>
       </c>
       <c r="BS34" s="2">
         <f t="shared" si="87"/>
-        <v>412553.34671999997</v>
+        <v>367346.4</v>
       </c>
       <c r="BT34" s="2">
         <f t="shared" si="87"/>
-        <v>581702.2078079998</v>
+        <v>518412.48239999998</v>
       </c>
       <c r="BU34" s="2">
         <f t="shared" ref="BU34" si="88">+BU32-BU33</f>
-        <v>758530.82519040001</v>
+        <v>676254.18216000008</v>
       </c>
       <c r="BV34" s="2">
         <f t="shared" ref="BV34" si="89">+BV32-BV33</f>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="BW34" s="2">
         <f t="shared" ref="BW34:DB34" si="90">BV34*(1+$BY$44)</f>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="BX34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="BY34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="BZ34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CA34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CB34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CC34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CD34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CE34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CF34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CG34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CH34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CI34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CJ34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CK34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CL34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CM34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CN34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CO34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CP34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CQ34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CR34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CS34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CT34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CU34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CV34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CW34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CX34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CY34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="CZ34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DA34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DB34" s="2">
         <f t="shared" si="90"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DC34" s="2">
         <f t="shared" ref="DC34:EH34" si="91">DB34*(1+$BY$44)</f>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DD34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DE34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DF34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DG34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DH34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DI34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DJ34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DK34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DL34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DM34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DN34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DO34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DP34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DQ34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DR34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DS34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DT34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DU34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DV34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DW34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DX34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DY34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="DZ34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EA34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EB34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EC34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="ED34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EE34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EF34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EG34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EH34" s="2">
         <f t="shared" si="91"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EI34" s="2">
         <f t="shared" ref="EI34:FN34" si="92">EH34*(1+$BY$44)</f>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EJ34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EK34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EL34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EM34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EN34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EO34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EP34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EQ34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="ER34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="ES34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="ET34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EU34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EV34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EW34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EX34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EY34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="EZ34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="FA34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="FB34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="FC34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="FD34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="FE34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="FF34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="FG34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="FH34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="FI34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="FJ34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="FK34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="FL34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="FM34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
       <c r="FN34" s="2">
         <f t="shared" si="92"/>
-        <v>988958.82591552008</v>
+        <v>881999.18997600023</v>
       </c>
     </row>
     <row r="35" spans="2:170" x14ac:dyDescent="0.25">
@@ -8116,23 +8116,23 @@
       </c>
       <c r="BR35" s="15">
         <f>+BR34/BR36</f>
-        <v>9.28385975647066</v>
+        <v>8.2408223704338237</v>
       </c>
       <c r="BS35" s="15">
         <f t="shared" si="107"/>
-        <v>16.828952118950006</v>
+        <v>14.984862020436886</v>
       </c>
       <c r="BT35" s="15">
         <f t="shared" si="107"/>
-        <v>23.728903620632678</v>
+        <v>21.147177482714312</v>
       </c>
       <c r="BU35" s="15">
         <f t="shared" ref="BU35:BV35" si="108">+BU34/BU36</f>
-        <v>30.942129155822066</v>
+        <v>27.58588517652818</v>
       </c>
       <c r="BV35" s="15">
         <f t="shared" si="108"/>
-        <v>40.341790610272291</v>
+        <v>35.978673437190245</v>
       </c>
       <c r="BW35" s="15"/>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="BR38" s="17">
         <f>+BR24/BQ24-1</f>
-        <v>0.89999999999999991</v>
+        <v>0.70262283996646757</v>
       </c>
       <c r="BS38" s="17">
         <f t="shared" si="133"/>
@@ -9702,8 +9702,8 @@
         <v>164</v>
       </c>
       <c r="BY46" s="2">
-        <f>NPV(BY45,BQ34:FN34)+Main!K5-Main!K6</f>
-        <v>10027994.742872769</v>
+        <f>NPV(BY45,BR34:FO34)+Main!K5-Main!K6+BQ34</f>
+        <v>9671049.1399095468</v>
       </c>
     </row>
     <row r="47" spans="2:170" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BY47" s="15">
         <f>BY46/Main!K3</f>
-        <v>412.67468077665717</v>
+        <v>397.98556131315007</v>
       </c>
     </row>
     <row r="48" spans="2:170" s="2" customFormat="1" x14ac:dyDescent="0.25">
